--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260612.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -601,66 +601,66 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ETN US</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>伊頓公開有限公司</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>46,066</t>
+          <t>87,630</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.10%</t>
+          <t>9.78%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>121,981</t>
+          <t>36,253</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>9.72%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ETN US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>伊頓公開有限公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>79,879</t>
+          <t>101,079</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.11%</t>
+          <t>8.73%</t>
         </is>
       </c>
     </row>
@@ -677,78 +677,78 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>36,898</t>
+          <t>39,788</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>8.03%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>Nextera Energy Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>39,713</t>
+          <t>218,390</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>54,564</t>
+          <t>116,148</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Nextera Energy Inc</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>147,552</t>
+          <t>54,828</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -765,359 +765,359 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>117,028</t>
+          <t>125,968</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>82,619</t>
+          <t>62,978</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>33,008</t>
+          <t>21,686</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NXT US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>NEXTracker公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>73,056</t>
+          <t>131,022</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>120,975</t>
+          <t>60,683</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>56,660</t>
+          <t>27,197</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>9,932</t>
+          <t>152,528</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,103</t>
+          <t>25,214</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>SWX US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>西南天然氣控股公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>65,675</t>
+          <t>69,720</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>51,099</t>
+          <t>12,687</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>15,048</t>
+          <t>55,658</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>107,418</t>
+          <t>41,158</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>53,029</t>
+          <t>57,306</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>18,120</t>
+          <t>36,381</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>54,509</t>
+          <t>86,169</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>34,552</t>
+          <t>56,020</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>14,428</t>
+          <t>34,069</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>53,140</t>
+          <t>24,908</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>129,716</t>
+          <t>52,626</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,83 +1173,83 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,370</t>
+          <t>5,507</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>31,595</t>
+          <t>23,174</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>11,297</t>
+          <t>30,851</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>41,875</t>
+          <t>14,830</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,396 +1261,396 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42,647</t>
+          <t>9,076</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>61,358</t>
+          <t>11,914</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>78,607</t>
+          <t>106,381</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>15,450</t>
+          <t>84,012</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>202606ESM6</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33,923</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>14,674</t>
+          <t>163,321</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>19,104</t>
+          <t>34,345</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>24,156</t>
+          <t>7,640</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>ENPH US</t>
+          <t>202606ESM6</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Enphase能源公司</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>31,476</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>16,932</t>
+          <t>48,660</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>21,448</t>
+          <t>28,850</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>OGE UN</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>OGE Energy Corp</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>29,002</t>
+          <t>6,577</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>77,540</t>
+          <t>15,022</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>18,188</t>
+          <t>18,047</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>29,949</t>
+          <t>105,753</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>ENPH US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Enphase能源公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>75,391</t>
+          <t>26,319</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>8,750</t>
+          <t>3,086</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>AMSC US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>美國超導公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>21,740</t>
+          <t>3,177</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1667,34 +1667,34 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>10,741</t>
+          <t>8,976</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MEI US</t>
+          <t>FLNC US</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>邁梭電子公司</t>
+          <t>通量能源公司</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>33,573</t>
+          <t>20,649</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1711,14 +1711,138 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>49,935</t>
+          <t>42,816</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
+          <t>0.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>MEI US</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>邁梭電子公司</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>NXT US</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>NEXTracker公司</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>OGE UN</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>OGE Energy Corp</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>SWX US</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>西南天然氣控股公司</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>AMSC US</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>美國超導公司</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>207,738,631</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
